--- a/Projet-Exemple/Generate Files/Bill of Materials/243-TGE-Lab1_PCB1_Capteurs.xlsx
+++ b/Projet-Exemple/Generate Files/Bill of Materials/243-TGE-Lab1_PCB1_Capteurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2233646\Desktop\dev\243-TEP_Altium-Lib\Projet-Exemple\Generate Files\Bill of Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D144E1F-0DDC-4D73-BBBB-928B5CF1C9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{504E99D6-25BE-446F-9616-9704D94466FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{78EFD804-B27D-4617-84AB-B5DF463F4BB2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B89227E2-1AF1-4C0A-80E2-451749808265}"/>
   </bookViews>
   <sheets>
     <sheet name="243-TGE-Lab1_PCB1_Capteurs" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="89">
   <si>
     <t>Code CEGEP</t>
   </si>
@@ -83,13 +83,13 @@
     <t>Supplier Part Number 2</t>
   </si>
   <si>
-    <t>KCOND01SM</t>
-  </si>
-  <si>
-    <t>CAP001</t>
-  </si>
-  <si>
-    <t>CAP CER 100nF 50V 0402</t>
+    <t>COND0143SM</t>
+  </si>
+  <si>
+    <t>CAP002</t>
+  </si>
+  <si>
+    <t>CAP CER 100nF 50V 0603</t>
   </si>
   <si>
     <t>C1, C2, C3</t>
@@ -101,13 +101,13 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>CC0402KRX7R9BB104</t>
+    <t>CC0603KRX7R9BB104</t>
   </si>
   <si>
     <t>LCSC</t>
   </si>
   <si>
-    <t>C131394</t>
+    <t>C14663</t>
   </si>
   <si>
     <t>CAP022</t>
@@ -173,58 +173,40 @@
     <t>SAM9303-ND</t>
   </si>
   <si>
-    <t>RES003</t>
-  </si>
-  <si>
-    <t>Res 10k 1% 0402</t>
-  </si>
-  <si>
-    <t>R1, R2</t>
+    <t>RESI0238-0603</t>
+  </si>
+  <si>
+    <t>RES001</t>
+  </si>
+  <si>
+    <t>Res 10k 1% 0603</t>
+  </si>
+  <si>
+    <t>R1, R2, R6, R7</t>
   </si>
   <si>
     <t>Resistor type 1</t>
   </si>
   <si>
-    <t>RC0402FR-0710KL</t>
-  </si>
-  <si>
-    <t>C60490</t>
-  </si>
-  <si>
-    <t>RES1KSM</t>
-  </si>
-  <si>
-    <t>RES006</t>
-  </si>
-  <si>
-    <t>Res 1k 1% 0402</t>
+    <t>RC0603FR-0710KL</t>
+  </si>
+  <si>
+    <t>C98220</t>
+  </si>
+  <si>
+    <t>RES015</t>
+  </si>
+  <si>
+    <t>Res 1k 1% 0603</t>
   </si>
   <si>
     <t>R3, R4, R25</t>
   </si>
   <si>
-    <t>RC0402FR-071kL</t>
-  </si>
-  <si>
-    <t>C106235</t>
-  </si>
-  <si>
-    <t>RESI0238-0603</t>
-  </si>
-  <si>
-    <t>RES001</t>
-  </si>
-  <si>
-    <t>Res 10k 1% 0603</t>
-  </si>
-  <si>
-    <t>R6, R7</t>
-  </si>
-  <si>
-    <t>RC0603FR-0710KL</t>
-  </si>
-  <si>
-    <t>C98220</t>
+    <t>RC0603FR-071KL</t>
+  </si>
+  <si>
+    <t>C22548</t>
   </si>
   <si>
     <t>RES029</t>
@@ -722,8 +704,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3BE152-9297-4A8E-8105-12C947BD7D1E}">
-  <dimension ref="A1:M13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708E9C2B-8FB2-4A74-AB7F-0675D468D547}">
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" customWidth="1"/>
@@ -930,42 +912,42 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>50</v>
@@ -980,7 +962,7 @@
         <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>18</v>
@@ -998,36 +980,34 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="1">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1036,25 +1016,25 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="1">
-        <v>16</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>20</v>
@@ -1062,155 +1042,122 @@
       <c r="K9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="L9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="J10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="J12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Projet-Exemple/Generate Files/Bill of Materials/243-TGE-Lab1_PCB1_Capteurs.xlsx
+++ b/Projet-Exemple/Generate Files/Bill of Materials/243-TGE-Lab1_PCB1_Capteurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2233646\Desktop\dev\243-TEP_Altium-Lib\Projet-Exemple\Generate Files\Bill of Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{504E99D6-25BE-446F-9616-9704D94466FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F77B6D3-3D1E-4CD4-ADFE-B2386C632E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B89227E2-1AF1-4C0A-80E2-451749808265}"/>
+    <workbookView xWindow="25080" yWindow="-5865" windowWidth="29040" windowHeight="15720" xr2:uid="{0CBAD05B-6AF0-4B63-8763-53C924A6C74B}"/>
   </bookViews>
   <sheets>
     <sheet name="243-TGE-Lab1_PCB1_Capteurs" sheetId="1" r:id="rId1"/>
@@ -704,7 +704,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708E9C2B-8FB2-4A74-AB7F-0675D468D547}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{344AAAE9-D51C-4312-8268-9D81025F4317}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
